--- a/data/umr/Resumen UMR Enero 2026.xlsx
+++ b/data/umr/Resumen UMR Enero 2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{D2CBAEE6-7553-4C58-8751-799888D50FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFA64AD1-C0B6-41C1-9EE8-7CEF48C22278}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{D2CBAEE6-7553-4C58-8751-799888D50FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1053A960-C676-41A3-B52C-A5AA30F61D36}"/>
   <bookViews>
-    <workbookView xWindow="4395" yWindow="4635" windowWidth="21600" windowHeight="11295" tabRatio="686" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Odometro-Kilometraje" sheetId="1" r:id="rId1"/>
@@ -4452,7 +4452,67 @@
     <xf numFmtId="0" fontId="0" fillId="60" borderId="85" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="53" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="53" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4468,9 +4528,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="76" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4491,51 +4548,6 @@
     <xf numFmtId="0" fontId="39" fillId="52" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4548,6 +4560,9 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4574,21 +4589,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="53" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="53" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5603,37 +5603,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="345" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="345"/>
-      <c r="C1" s="345"/>
-      <c r="D1" s="345"/>
-      <c r="E1" s="345"/>
-      <c r="F1" s="345"/>
-      <c r="G1" s="345"/>
-      <c r="H1" s="345"/>
-      <c r="I1" s="345"/>
-      <c r="J1" s="345"/>
-      <c r="K1" s="345"/>
-      <c r="L1" s="345"/>
-      <c r="M1" s="345"/>
-      <c r="N1" s="345"/>
-      <c r="O1" s="345"/>
-      <c r="P1" s="345"/>
-      <c r="Q1" s="345"/>
-      <c r="R1" s="345"/>
-      <c r="S1" s="345"/>
-      <c r="T1" s="345"/>
-      <c r="U1" s="345"/>
-      <c r="V1" s="345"/>
-      <c r="W1" s="345"/>
-      <c r="X1" s="345"/>
-      <c r="Y1" s="345"/>
-      <c r="Z1" s="345"/>
-      <c r="AA1" s="345"/>
-      <c r="AB1" s="345"/>
-      <c r="AC1" s="345"/>
+      <c r="A1" s="349" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="349"/>
+      <c r="C1" s="349"/>
+      <c r="D1" s="349"/>
+      <c r="E1" s="349"/>
+      <c r="F1" s="349"/>
+      <c r="G1" s="349"/>
+      <c r="H1" s="349"/>
+      <c r="I1" s="349"/>
+      <c r="J1" s="349"/>
+      <c r="K1" s="349"/>
+      <c r="L1" s="349"/>
+      <c r="M1" s="349"/>
+      <c r="N1" s="349"/>
+      <c r="O1" s="349"/>
+      <c r="P1" s="349"/>
+      <c r="Q1" s="349"/>
+      <c r="R1" s="349"/>
+      <c r="S1" s="349"/>
+      <c r="T1" s="349"/>
+      <c r="U1" s="349"/>
+      <c r="V1" s="349"/>
+      <c r="W1" s="349"/>
+      <c r="X1" s="349"/>
+      <c r="Y1" s="349"/>
+      <c r="Z1" s="349"/>
+      <c r="AA1" s="349"/>
+      <c r="AB1" s="349"/>
+      <c r="AC1" s="349"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -9386,37 +9386,37 @@
       <c r="AC40" s="213"/>
     </row>
     <row r="41" spans="1:32" ht="18" x14ac:dyDescent="0.25">
-      <c r="A41" s="345" t="s">
+      <c r="A41" s="349" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="345"/>
-      <c r="C41" s="345"/>
-      <c r="D41" s="345"/>
-      <c r="E41" s="345"/>
-      <c r="F41" s="345"/>
-      <c r="G41" s="345"/>
-      <c r="H41" s="345"/>
-      <c r="I41" s="345"/>
-      <c r="J41" s="345"/>
-      <c r="K41" s="345"/>
-      <c r="L41" s="345"/>
-      <c r="M41" s="345"/>
-      <c r="N41" s="345"/>
-      <c r="O41" s="345"/>
-      <c r="P41" s="345"/>
-      <c r="Q41" s="345"/>
-      <c r="R41" s="345"/>
-      <c r="S41" s="345"/>
-      <c r="T41" s="345"/>
-      <c r="U41" s="345"/>
-      <c r="V41" s="345"/>
-      <c r="W41" s="345"/>
-      <c r="X41" s="345"/>
-      <c r="Y41" s="345"/>
-      <c r="Z41" s="345"/>
-      <c r="AA41" s="345"/>
-      <c r="AB41" s="345"/>
-      <c r="AC41" s="345"/>
+      <c r="B41" s="349"/>
+      <c r="C41" s="349"/>
+      <c r="D41" s="349"/>
+      <c r="E41" s="349"/>
+      <c r="F41" s="349"/>
+      <c r="G41" s="349"/>
+      <c r="H41" s="349"/>
+      <c r="I41" s="349"/>
+      <c r="J41" s="349"/>
+      <c r="K41" s="349"/>
+      <c r="L41" s="349"/>
+      <c r="M41" s="349"/>
+      <c r="N41" s="349"/>
+      <c r="O41" s="349"/>
+      <c r="P41" s="349"/>
+      <c r="Q41" s="349"/>
+      <c r="R41" s="349"/>
+      <c r="S41" s="349"/>
+      <c r="T41" s="349"/>
+      <c r="U41" s="349"/>
+      <c r="V41" s="349"/>
+      <c r="W41" s="349"/>
+      <c r="X41" s="349"/>
+      <c r="Y41" s="349"/>
+      <c r="Z41" s="349"/>
+      <c r="AA41" s="349"/>
+      <c r="AB41" s="349"/>
+      <c r="AC41" s="349"/>
       <c r="AF41" s="124"/>
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.25">
@@ -14608,51 +14608,51 @@
         <v>40</v>
       </c>
       <c r="E3" s="365"/>
-      <c r="F3" s="358" t="s">
+      <c r="F3" s="356" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="358" t="s">
+      <c r="G3" s="356" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="358" t="s">
+      <c r="H3" s="356" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="358" t="s">
+      <c r="I3" s="356" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="358" t="s">
+      <c r="J3" s="356" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="358" t="s">
+      <c r="K3" s="356" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="358" t="s">
+      <c r="L3" s="356" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="358" t="s">
+      <c r="M3" s="356" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="351" t="s">
+      <c r="N3" s="363" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="351" t="s">
+      <c r="O3" s="363" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="350"/>
-      <c r="Q3" s="352" t="s">
+      <c r="P3" s="370"/>
+      <c r="Q3" s="371" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="353"/>
-      <c r="S3" s="354"/>
-      <c r="T3" s="355" t="s">
+      <c r="R3" s="372"/>
+      <c r="S3" s="373"/>
+      <c r="T3" s="374" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="356"/>
-      <c r="V3" s="357"/>
-      <c r="W3" s="348" t="s">
+      <c r="U3" s="375"/>
+      <c r="V3" s="376"/>
+      <c r="W3" s="368" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="348" t="s">
+      <c r="X3" s="368" t="s">
         <v>162</v>
       </c>
     </row>
@@ -14670,17 +14670,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="358"/>
-      <c r="G4" s="366"/>
-      <c r="H4" s="366"/>
-      <c r="I4" s="358"/>
-      <c r="J4" s="358"/>
-      <c r="K4" s="358"/>
-      <c r="L4" s="358"/>
-      <c r="M4" s="358"/>
-      <c r="N4" s="351"/>
-      <c r="O4" s="351"/>
-      <c r="P4" s="350"/>
+      <c r="F4" s="356"/>
+      <c r="G4" s="357"/>
+      <c r="H4" s="357"/>
+      <c r="I4" s="356"/>
+      <c r="J4" s="356"/>
+      <c r="K4" s="356"/>
+      <c r="L4" s="356"/>
+      <c r="M4" s="356"/>
+      <c r="N4" s="363"/>
+      <c r="O4" s="363"/>
+      <c r="P4" s="370"/>
       <c r="Q4" s="195" t="s">
         <v>140</v>
       </c>
@@ -14699,8 +14699,8 @@
       <c r="V4" s="238" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="349"/>
-      <c r="X4" s="349"/>
+      <c r="W4" s="369"/>
+      <c r="X4" s="369"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -15499,7 +15499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="203"/>
       <c r="B17" s="299">
         <v>1</v>
@@ -15564,7 +15564,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20"/>
       <c r="B18" s="119">
         <f>SUM(B12:B17)</f>
@@ -15595,8 +15595,8 @@
         <f t="shared" si="11"/>
         <v>223</v>
       </c>
-      <c r="J18" s="119">
-        <f t="shared" si="11"/>
+      <c r="J18" s="120">
+        <f>SUM(J12:J17)</f>
         <v>11492.41</v>
       </c>
       <c r="K18" s="119">
@@ -15634,8 +15634,9 @@
         <f>SUM(X12:X17)</f>
         <v>11492.41</v>
       </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Z18" s="342"/>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="60">
         <f>A12+1</f>
         <v>46025</v>
@@ -15703,7 +15704,7 @@
         <v>3234.75</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="218"/>
       <c r="B20" s="116">
         <v>75</v>
@@ -15768,7 +15769,7 @@
         <v>3234.75</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="218"/>
       <c r="B21" s="116">
         <v>0</v>
@@ -15833,7 +15834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="218"/>
       <c r="B22" s="116">
         <v>0</v>
@@ -15898,7 +15899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="218"/>
       <c r="B23" s="116">
         <v>0</v>
@@ -15963,7 +15964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="218"/>
       <c r="B24" s="116">
         <v>0</v>
@@ -16028,7 +16029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20"/>
       <c r="B25" s="119">
         <f>SUM(B19:B24)</f>
@@ -16098,8 +16099,9 @@
         <f>SUM(X19:X24)</f>
         <v>6469.5</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Z25" s="342"/>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="60">
         <f>A19+1</f>
         <v>46026</v>
@@ -16167,7 +16169,7 @@
         <v>2458.4100000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="218"/>
       <c r="B27" s="220">
         <v>57</v>
@@ -16224,7 +16226,7 @@
       <c r="U27" s="219"/>
       <c r="V27" s="231"/>
       <c r="W27" s="186">
-        <f>J27-(T27*($M$2-$K$1)+(U27*($M$2-$M$1))+(V27*($M$2-$I$2)))</f>
+        <f>J27-(T27*($M$2-$K$1)+(U27*($M$2-$M$1)))</f>
         <v>2458.4100000000003</v>
       </c>
       <c r="X27" s="183">
@@ -16232,7 +16234,7 @@
         <v>2458.4100000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="218"/>
       <c r="B28" s="220">
         <v>0</v>
@@ -16297,7 +16299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="218"/>
       <c r="B29" s="220">
         <v>0</v>
@@ -16362,7 +16364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="218"/>
       <c r="B30" s="220">
         <v>0</v>
@@ -16426,7 +16428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="218"/>
       <c r="B31" s="220">
         <v>0</v>
@@ -16490,7 +16492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20"/>
       <c r="B32" s="119">
         <f>SUM(B26:B31)</f>
@@ -16560,6 +16562,7 @@
         <f>SUM(X26:X31)</f>
         <v>4916.8200000000006</v>
       </c>
+      <c r="Z32" s="342"/>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="60">
@@ -16690,7 +16693,7 @@
       <c r="U34" s="219"/>
       <c r="V34" s="231"/>
       <c r="W34" s="186">
-        <f>J34-(T34*($M$2-$K$1)+(U34*($M$2-$M$1))+(V34*($M$2-$I$2)))</f>
+        <f>J34-(T34*($M$2-$K$1)+(U34*($M$2-$M$1)))</f>
         <v>4769.7000000000007</v>
       </c>
       <c r="X34" s="183">
@@ -16990,7 +16993,7 @@
         <v>223</v>
       </c>
       <c r="J39" s="120">
-        <f t="shared" si="29"/>
+        <f>SUM(J33:J38)</f>
         <v>11492.41</v>
       </c>
       <c r="K39" s="119">
@@ -17028,6 +17031,7 @@
         <f>SUM(X33:X38)</f>
         <v>11492.41</v>
       </c>
+      <c r="Z39" s="342"/>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="60">
@@ -17486,7 +17490,7 @@
         <v>223</v>
       </c>
       <c r="J46" s="120">
-        <f t="shared" si="35"/>
+        <f>SUM(J40:J45)</f>
         <v>11492.41</v>
       </c>
       <c r="K46" s="119">
@@ -17524,7 +17528,7 @@
         <f>SUM(X40:X45)</f>
         <v>11492.41</v>
       </c>
-      <c r="Z46" s="257"/>
+      <c r="Z46" s="342"/>
       <c r="AA46" s="257"/>
       <c r="AB46" s="257"/>
       <c r="AC46" s="257"/>
@@ -17594,8 +17598,8 @@
       <c r="U47" s="192"/>
       <c r="V47" s="230"/>
       <c r="W47" s="183">
-        <f>J47-(Q47*($M$2-$K$1))-(R47*($M$2-$M$1))- (S47*($M$2-$I$2))+ (T47*($G$2))-128.58</f>
-        <v>4641.1200000000008</v>
+        <f>J47-(Q47*($M$2-$K$1))-(R47*($M$2-$M$1))- (S47*($M$2-$I$2))+ (T47*($G$2))</f>
+        <v>4769.7000000000007</v>
       </c>
       <c r="X47" s="183">
         <f>H47*$M$2</f>
@@ -17665,8 +17669,8 @@
       <c r="U48" s="219"/>
       <c r="V48" s="231"/>
       <c r="W48" s="186">
-        <f>J48-(T48*($M$2-$K$1)+(U48*($M$2-$M$1)))-150.01</f>
-        <v>4447.17</v>
+        <f>J48-(T48*($M$2-$K$1)+(U48*($M$2-$M$1)))</f>
+        <v>4597.18</v>
       </c>
       <c r="X48" s="183">
         <f>H48*$M$2</f>
@@ -17676,7 +17680,7 @@
       <c r="AC48" s="124"/>
     </row>
     <row r="49" spans="1:65" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="367" t="s">
+      <c r="A49" s="350" t="s">
         <v>178</v>
       </c>
       <c r="B49" s="299">
@@ -17743,7 +17747,7 @@
       </c>
     </row>
     <row r="50" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A50" s="367"/>
+      <c r="A50" s="350"/>
       <c r="B50" s="299">
         <v>32</v>
       </c>
@@ -17808,7 +17812,7 @@
       </c>
     </row>
     <row r="51" spans="1:65" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="367"/>
+      <c r="A51" s="350"/>
       <c r="B51" s="299">
         <v>0</v>
       </c>
@@ -17969,7 +17973,7 @@
         <v>221</v>
       </c>
       <c r="J53" s="120">
-        <f t="shared" si="41"/>
+        <f>SUM(J47:J52)</f>
         <v>11378.109999999999</v>
       </c>
       <c r="K53" s="119">
@@ -17990,7 +17994,7 @@
       </c>
       <c r="O53" s="21">
         <f>(W53/N53)*100</f>
-        <v>92.983107824186902</v>
+        <v>95.324397008151934</v>
       </c>
       <c r="P53" s="193"/>
       <c r="Q53" s="182"/>
@@ -18001,12 +18005,13 @@
       <c r="V53" s="182"/>
       <c r="W53" s="194">
         <f>SUM(W47:W52)</f>
-        <v>11064.06</v>
+        <v>11342.65</v>
       </c>
       <c r="X53" s="194">
         <f>SUM(X47:X52)</f>
         <v>11492.41</v>
       </c>
+      <c r="Z53" s="342"/>
     </row>
     <row r="54" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A54" s="60">
@@ -18079,7 +18084,7 @@
       </c>
     </row>
     <row r="55" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="367" t="s">
+      <c r="A55" s="350" t="s">
         <v>182</v>
       </c>
       <c r="B55" s="299">
@@ -18148,7 +18153,7 @@
       </c>
     </row>
     <row r="56" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="367"/>
+      <c r="A56" s="350"/>
       <c r="B56" s="299">
         <v>33</v>
       </c>
@@ -18213,7 +18218,7 @@
       </c>
     </row>
     <row r="57" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="367"/>
+      <c r="A57" s="350"/>
       <c r="B57" s="299">
         <v>32</v>
       </c>
@@ -18281,7 +18286,7 @@
       </c>
     </row>
     <row r="58" spans="1:65" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="367"/>
+      <c r="A58" s="350"/>
       <c r="B58" s="299">
         <v>0</v>
       </c>
@@ -18346,7 +18351,7 @@
       </c>
     </row>
     <row r="59" spans="1:65" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="367"/>
+      <c r="A59" s="350"/>
       <c r="B59" s="299">
         <v>1</v>
       </c>
@@ -18442,7 +18447,7 @@
         <v>225</v>
       </c>
       <c r="J60" s="120">
-        <f t="shared" si="47"/>
+        <f>SUM(J54:J59)</f>
         <v>11681.09</v>
       </c>
       <c r="K60" s="119">
@@ -18480,6 +18485,7 @@
         <f>SUM(X54:X59)</f>
         <v>11492.41</v>
       </c>
+      <c r="Z60" s="342"/>
     </row>
     <row r="61" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A61" s="60">
@@ -18916,7 +18922,7 @@
         <v>223</v>
       </c>
       <c r="J67" s="120">
-        <f t="shared" si="53"/>
+        <f>SUM(J61:J66)</f>
         <v>11667.07</v>
       </c>
       <c r="K67" s="119">
@@ -18955,6 +18961,7 @@
         <v>11492.41</v>
       </c>
       <c r="Y67" s="240"/>
+      <c r="Z67" s="342"/>
     </row>
     <row r="68" spans="1:27" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="60">
@@ -19081,7 +19088,7 @@
       <c r="U69" s="219"/>
       <c r="V69" s="231"/>
       <c r="W69" s="186">
-        <f>J69-(T69*($M$2-$K$1)+(U69*($M$2-$M$1))+(V69*($U$2)))</f>
+        <f>J69-(T69*($M$2-$K$1)+(U69*($M$2-$M$1)))</f>
         <v>3234.75</v>
       </c>
       <c r="X69" s="183">
@@ -19384,7 +19391,8 @@
         <v>147</v>
       </c>
       <c r="J74" s="120">
-        <v>11514.1</v>
+        <f t="shared" si="59"/>
+        <v>6469.5</v>
       </c>
       <c r="K74" s="119">
         <f t="shared" si="59"/>
@@ -19422,7 +19430,7 @@
         <v>6469.5</v>
       </c>
       <c r="Y74" s="257"/>
-      <c r="Z74" s="257"/>
+      <c r="Z74" s="342"/>
       <c r="AA74" s="257"/>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.25">
@@ -19911,7 +19919,7 @@
         <v>4916.8200000000006</v>
       </c>
       <c r="Y81" s="257"/>
-      <c r="Z81" s="257"/>
+      <c r="Z81" s="342"/>
       <c r="AA81" s="257"/>
       <c r="AD81" s="172"/>
     </row>
@@ -20359,7 +20367,7 @@
         <v>223</v>
       </c>
       <c r="J88" s="120">
-        <f t="shared" si="71"/>
+        <f>SUM(J82:J87)</f>
         <v>11492.41</v>
       </c>
       <c r="K88" s="119">
@@ -20397,6 +20405,7 @@
         <f>SUM(X82:X87)</f>
         <v>11492.41</v>
       </c>
+      <c r="Z88" s="342"/>
       <c r="AA88" s="172"/>
     </row>
     <row r="89" spans="1:30" x14ac:dyDescent="0.25">
@@ -20470,7 +20479,7 @@
       </c>
     </row>
     <row r="90" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="370" t="s">
+      <c r="A90" s="358" t="s">
         <v>183</v>
       </c>
       <c r="B90" s="299">
@@ -20539,7 +20548,7 @@
       </c>
     </row>
     <row r="91" spans="1:30" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="370"/>
+      <c r="A91" s="358"/>
       <c r="B91" s="299">
         <v>33</v>
       </c>
@@ -20595,8 +20604,8 @@
       <c r="U91" s="190"/>
       <c r="V91" s="190"/>
       <c r="W91" s="183">
-        <f>J91-(Q91*($M$1-$K$1))-7.68-18.84</f>
-        <v>584.79</v>
+        <f>J91-(Q91*($M$1-$K$1))</f>
+        <v>611.30999999999995</v>
       </c>
       <c r="X91" s="183">
         <f>H91*$M$1</f>
@@ -20604,7 +20613,7 @@
       </c>
     </row>
     <row r="92" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="370"/>
+      <c r="A92" s="358"/>
       <c r="B92" s="299">
         <v>32</v>
       </c>
@@ -20669,7 +20678,7 @@
       </c>
     </row>
     <row r="93" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="370"/>
+      <c r="A93" s="358"/>
       <c r="B93" s="299">
         <v>0</v>
       </c>
@@ -20735,7 +20744,7 @@
       <c r="AB93" s="124"/>
     </row>
     <row r="94" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="371"/>
+      <c r="A94" s="359"/>
       <c r="B94" s="299">
         <v>1</v>
       </c>
@@ -20831,7 +20840,7 @@
         <v>203</v>
       </c>
       <c r="J95" s="120">
-        <f t="shared" si="77"/>
+        <f>SUM(J89:J94)</f>
         <v>9903.1299999999992</v>
       </c>
       <c r="K95" s="119">
@@ -20852,7 +20861,7 @@
       </c>
       <c r="O95" s="21">
         <f>(W95/N95)*100</f>
-        <v>94.52867590454197</v>
+        <v>94.783872209391845</v>
       </c>
       <c r="P95" s="193"/>
       <c r="Q95" s="251"/>
@@ -20863,12 +20872,13 @@
       <c r="V95" s="182"/>
       <c r="W95" s="194">
         <f>SUM(W89:W94)</f>
-        <v>9823.4200000000019</v>
+        <v>9849.94</v>
       </c>
       <c r="X95" s="194">
         <f>SUM(X89:X94)</f>
         <v>10716.07</v>
       </c>
+      <c r="Z95" s="342"/>
     </row>
     <row r="96" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="60">
@@ -21299,7 +21309,7 @@
         <v>223</v>
       </c>
       <c r="J102" s="120">
-        <f t="shared" si="83"/>
+        <f>SUM(J96:J101)</f>
         <v>10716.07</v>
       </c>
       <c r="K102" s="119">
@@ -21337,6 +21347,7 @@
         <f>SUM(X96:X101)</f>
         <v>10716.07</v>
       </c>
+      <c r="Z102" s="342"/>
       <c r="AA102" s="172"/>
       <c r="AD102"/>
     </row>
@@ -21769,7 +21780,7 @@
         <v>223</v>
       </c>
       <c r="J109" s="120">
-        <f t="shared" si="89"/>
+        <f>SUM(J103:J108)</f>
         <v>10716.07</v>
       </c>
       <c r="K109" s="119">
@@ -21807,6 +21818,7 @@
         <f>SUM(X103:X108)</f>
         <v>10716.07</v>
       </c>
+      <c r="Z109" s="342"/>
     </row>
     <row r="110" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="60">
@@ -22238,7 +22250,7 @@
         <v>223</v>
       </c>
       <c r="J116" s="120">
-        <f t="shared" si="95"/>
+        <f>SUM(J110:J115)</f>
         <v>10629.81</v>
       </c>
       <c r="K116" s="119">
@@ -22276,6 +22288,7 @@
         <f>SUM(X110:X115)</f>
         <v>10716.07</v>
       </c>
+      <c r="Z116" s="342"/>
     </row>
     <row r="117" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="60">
@@ -22742,6 +22755,7 @@
         <f>SUM(X117:X122)</f>
         <v>6469.5</v>
       </c>
+      <c r="Z123" s="342"/>
     </row>
     <row r="124" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="60">
@@ -22867,8 +22881,8 @@
       <c r="T125" s="184"/>
       <c r="U125" s="219"/>
       <c r="V125" s="231"/>
-      <c r="W125" s="183">
-        <f>J125-(Q125*($K$1)+(T125*($M$2-$K$1))+(U125*($M$2-$M$1)))</f>
+      <c r="W125" s="186">
+        <f>J125-(T125*($M$2-$K$1)+(U125*($M$2-$M$1)))</f>
         <v>2458.4100000000003</v>
       </c>
       <c r="X125" s="183">
@@ -23071,7 +23085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:26" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="255"/>
       <c r="B129" s="220">
         <v>0</v>
@@ -23136,7 +23150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:26" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="20"/>
       <c r="B130" s="119">
         <f>SUM(B124:B129)</f>
@@ -23206,8 +23220,9 @@
         <f>SUM(X124:X129)</f>
         <v>4830.5600000000004</v>
       </c>
-    </row>
-    <row r="131" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z130" s="342"/>
+    </row>
+    <row r="131" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="60">
         <f>A124+1</f>
         <v>46041</v>
@@ -23277,7 +23292,7 @@
         <v>4399.26</v>
       </c>
     </row>
-    <row r="132" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="255"/>
       <c r="B132" s="299">
         <v>54</v>
@@ -23344,7 +23359,7 @@
         <v>4399.26</v>
       </c>
     </row>
-    <row r="133" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="255"/>
       <c r="B133" s="299">
         <v>33</v>
@@ -23409,7 +23424,7 @@
         <v>960.63</v>
       </c>
     </row>
-    <row r="134" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="255"/>
       <c r="B134" s="299">
         <v>32</v>
@@ -23474,7 +23489,7 @@
         <v>931.52</v>
       </c>
     </row>
-    <row r="135" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="255"/>
       <c r="B135" s="299">
         <v>0</v>
@@ -23539,7 +23554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="255"/>
       <c r="B136" s="299">
         <v>1</v>
@@ -23604,7 +23619,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="137" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:26" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="20"/>
       <c r="B137" s="119">
         <f>SUM(B131:B136)</f>
@@ -23636,7 +23651,7 @@
         <v>223</v>
       </c>
       <c r="J137" s="120">
-        <f t="shared" si="113"/>
+        <f>SUM(J131:J136)</f>
         <v>10716.07</v>
       </c>
       <c r="K137" s="119">
@@ -23674,8 +23689,9 @@
         <f>SUM(X131:X136)</f>
         <v>10716.07</v>
       </c>
-    </row>
-    <row r="138" spans="1:24" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z137" s="342"/>
+    </row>
+    <row r="138" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="60">
         <f>A131+1</f>
         <v>46042</v>
@@ -23745,7 +23761,7 @@
         <v>4399.26</v>
       </c>
     </row>
-    <row r="139" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="255"/>
       <c r="B139" s="299">
         <v>54</v>
@@ -23812,7 +23828,7 @@
         <v>4399.26</v>
       </c>
     </row>
-    <row r="140" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="255"/>
       <c r="B140" s="299">
         <v>33</v>
@@ -23877,7 +23893,7 @@
         <v>960.63</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="255"/>
       <c r="B141" s="299">
         <v>32</v>
@@ -23942,7 +23958,7 @@
         <v>931.52</v>
       </c>
     </row>
-    <row r="142" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="255"/>
       <c r="B142" s="299">
         <v>0</v>
@@ -24007,7 +24023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="255"/>
       <c r="B143" s="299">
         <v>1</v>
@@ -24072,7 +24088,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="144" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:26" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="20"/>
       <c r="B144" s="119">
         <f>SUM(B138:B143)</f>
@@ -24104,7 +24120,7 @@
         <v>223</v>
       </c>
       <c r="J144" s="120">
-        <f t="shared" si="119"/>
+        <f>SUM(J138:J143)</f>
         <v>10716.07</v>
       </c>
       <c r="K144" s="119">
@@ -24142,6 +24158,7 @@
         <f>SUM(X138:X143)</f>
         <v>10716.07</v>
       </c>
+      <c r="Z144" s="342"/>
     </row>
     <row r="145" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A145" s="60">
@@ -24610,6 +24627,7 @@
         <f>SUM(X145:X150)</f>
         <v>10716.07</v>
       </c>
+      <c r="Z151" s="342"/>
     </row>
     <row r="152" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A152" s="60">
@@ -25048,7 +25066,7 @@
         <v>223</v>
       </c>
       <c r="J158" s="120">
-        <f t="shared" si="131"/>
+        <f>SUM(J152:J157)</f>
         <v>10716.07</v>
       </c>
       <c r="K158" s="119">
@@ -25086,6 +25104,7 @@
         <f>SUM(X152:X157)</f>
         <v>10716.07</v>
       </c>
+      <c r="Z158" s="342"/>
     </row>
     <row r="159" spans="1:26" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="60">
@@ -25158,7 +25177,7 @@
       </c>
     </row>
     <row r="160" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="367" t="s">
+      <c r="A160" s="350" t="s">
         <v>184</v>
       </c>
       <c r="B160" s="299">
@@ -25227,8 +25246,8 @@
       </c>
       <c r="Y160" s="172"/>
     </row>
-    <row r="161" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="367"/>
+    <row r="161" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="350"/>
       <c r="B161" s="299">
         <v>33</v>
       </c>
@@ -25292,8 +25311,8 @@
         <v>960.63</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="367"/>
+    <row r="162" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="350"/>
       <c r="B162" s="299">
         <v>32</v>
       </c>
@@ -25357,8 +25376,8 @@
         <v>931.52</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="367"/>
+    <row r="163" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="350"/>
       <c r="B163" s="299">
         <v>0</v>
       </c>
@@ -25422,8 +25441,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="12.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="367"/>
+    <row r="164" spans="1:26" ht="12.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="350"/>
       <c r="B164" s="299">
         <v>1</v>
       </c>
@@ -25487,7 +25506,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="165" spans="1:25" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:26" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="341"/>
       <c r="B165" s="119">
         <f>SUM(B159:B164)</f>
@@ -25519,7 +25538,7 @@
         <v>217</v>
       </c>
       <c r="J165" s="120">
-        <f t="shared" si="137"/>
+        <f>SUM(J159:J164)</f>
         <v>10392.969999999999</v>
       </c>
       <c r="K165" s="119">
@@ -25557,8 +25576,9 @@
         <f>SUM(X159:X164)</f>
         <v>10716.07</v>
       </c>
-    </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z165" s="342"/>
+    </row>
+    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A166" s="60">
         <f>A159+1</f>
         <v>46046</v>
@@ -25626,7 +25646,7 @@
         <v>3234.75</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="255"/>
       <c r="B167" s="116">
         <v>75</v>
@@ -25692,7 +25712,7 @@
       </c>
       <c r="Y167" s="172"/>
     </row>
-    <row r="168" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="255"/>
       <c r="B168" s="116">
         <v>0</v>
@@ -25757,7 +25777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="255"/>
       <c r="B169" s="116">
         <v>0</v>
@@ -25822,7 +25842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="255"/>
       <c r="B170" s="116">
         <v>0</v>
@@ -25887,7 +25907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="255"/>
       <c r="B171" s="116">
         <v>0</v>
@@ -25952,7 +25972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:25" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:26" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="20"/>
       <c r="B172" s="119">
         <f>SUM(B166:B171)</f>
@@ -26022,8 +26042,9 @@
         <f>SUM(X166:X171)</f>
         <v>6469.5</v>
       </c>
-    </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z172" s="342"/>
+    </row>
+    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A173" s="60">
         <f>A166+1</f>
         <v>46047</v>
@@ -26091,7 +26112,7 @@
         <v>2458.4100000000003</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="203"/>
       <c r="B174" s="220">
         <v>57</v>
@@ -26157,7 +26178,7 @@
       </c>
       <c r="Y174" s="172"/>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A175" s="203"/>
       <c r="B175" s="220">
         <v>0</v>
@@ -26222,7 +26243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="203"/>
       <c r="B176" s="220">
         <v>0</v>
@@ -26487,6 +26508,7 @@
         <f>SUM(X173:X178)</f>
         <v>4916.8200000000006</v>
       </c>
+      <c r="Z179" s="342"/>
     </row>
     <row r="180" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A180" s="60">
@@ -26564,7 +26586,7 @@
       <c r="AD180" s="124"/>
     </row>
     <row r="181" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="372" t="s">
+      <c r="A181" s="360" t="s">
         <v>179</v>
       </c>
       <c r="B181" s="299">
@@ -26623,8 +26645,8 @@
       </c>
       <c r="U181" s="219"/>
       <c r="V181" s="207"/>
-      <c r="W181" s="183">
-        <f>J181-(Q181*($K$1)+(T181*($M$2-$K$1))+(U181*($M$2-$M$1)))</f>
+      <c r="W181" s="186">
+        <f>J181-(T181*($M$2-$K$1)+(U181*($M$2-$M$1)))</f>
         <v>4044.1600000000003</v>
       </c>
       <c r="X181" s="183">
@@ -26638,7 +26660,7 @@
       <c r="AD181" s="124"/>
     </row>
     <row r="182" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A182" s="372"/>
+      <c r="A182" s="360"/>
       <c r="B182" s="299">
         <v>33</v>
       </c>
@@ -26705,7 +26727,7 @@
       </c>
     </row>
     <row r="183" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="372"/>
+      <c r="A183" s="360"/>
       <c r="B183" s="299">
         <v>32</v>
       </c>
@@ -26770,7 +26792,7 @@
       </c>
     </row>
     <row r="184" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="372"/>
+      <c r="A184" s="360"/>
       <c r="B184" s="299">
         <v>0</v>
       </c>
@@ -26835,7 +26857,7 @@
       </c>
     </row>
     <row r="185" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="372"/>
+      <c r="A185" s="360"/>
       <c r="B185" s="299">
         <v>1</v>
       </c>
@@ -26931,7 +26953,7 @@
         <v>223</v>
       </c>
       <c r="J186" s="120">
-        <f t="shared" si="155"/>
+        <f>SUM(J180:J185)</f>
         <v>10112.25</v>
       </c>
       <c r="K186" s="119">
@@ -26969,6 +26991,7 @@
         <f>SUM(X180:X185)</f>
         <v>10198.51</v>
       </c>
+      <c r="Z186" s="342"/>
     </row>
     <row r="187" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A187" s="60">
@@ -27367,7 +27390,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="193" spans="1:25" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:26" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="20"/>
       <c r="B193" s="119">
         <f>SUM(B187:B192)</f>
@@ -27398,8 +27421,8 @@
         <f t="shared" si="161"/>
         <v>223</v>
       </c>
-      <c r="J193" s="119">
-        <f t="shared" si="161"/>
+      <c r="J193" s="120">
+        <f>SUM(J187:J192)</f>
         <v>10198.51</v>
       </c>
       <c r="K193" s="119">
@@ -27437,8 +27460,9 @@
         <f>SUM(X187:X192)</f>
         <v>10198.51</v>
       </c>
-    </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z193" s="342"/>
+    </row>
+    <row r="194" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A194" s="60">
         <f>A187+1</f>
         <v>46050</v>
@@ -27508,7 +27532,7 @@
         <v>4140.4800000000005</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="203"/>
       <c r="B195" s="299">
         <v>60</v>
@@ -27575,7 +27599,7 @@
         <v>4140.4800000000005</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="203"/>
       <c r="B196" s="299">
         <v>33</v>
@@ -27642,7 +27666,7 @@
         <v>960.63</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="203"/>
       <c r="B197" s="299">
         <v>32</v>
@@ -27709,7 +27733,7 @@
         <v>931.52</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="203"/>
       <c r="B198" s="299">
         <v>0</v>
@@ -27774,7 +27798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="203"/>
       <c r="B199" s="299">
         <v>1</v>
@@ -27839,7 +27863,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="200" spans="1:25" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:26" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="20"/>
       <c r="B200" s="119">
         <f>SUM(B194:B199)</f>
@@ -27870,8 +27894,8 @@
         <f t="shared" si="167"/>
         <v>223</v>
       </c>
-      <c r="J200" s="119">
-        <f t="shared" si="167"/>
+      <c r="J200" s="120">
+        <f>SUM(J194:J199)</f>
         <v>10198.51</v>
       </c>
       <c r="K200" s="119">
@@ -27909,8 +27933,9 @@
         <f>SUM(X194:X199)</f>
         <v>10198.51</v>
       </c>
-    </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z200" s="342"/>
+    </row>
+    <row r="201" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A201" s="60">
         <f>A194+1</f>
         <v>46051</v>
@@ -27980,7 +28005,7 @@
         <v>4140.4800000000005</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="203"/>
       <c r="B202" s="299">
         <v>60</v>
@@ -28047,7 +28072,7 @@
         <v>4140.4800000000005</v>
       </c>
     </row>
-    <row r="203" spans="1:25" s="124" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:26" s="124" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="203"/>
       <c r="B203" s="299">
         <v>33</v>
@@ -28114,7 +28139,7 @@
         <v>960.63</v>
       </c>
     </row>
-    <row r="204" spans="1:25" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:26" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="203"/>
       <c r="B204" s="299">
         <v>32</v>
@@ -28181,7 +28206,7 @@
         <v>931.52</v>
       </c>
     </row>
-    <row r="205" spans="1:25" s="124" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:26" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="203"/>
       <c r="B205" s="299">
         <v>0</v>
@@ -28246,7 +28271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:25" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:26" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="203"/>
       <c r="B206" s="299">
         <v>1</v>
@@ -28311,7 +28336,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="207" spans="1:25" s="124" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:26" s="124" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="20"/>
       <c r="B207" s="119">
         <f>SUM(B201:B206)</f>
@@ -28343,7 +28368,7 @@
         <v>223</v>
       </c>
       <c r="J207" s="120">
-        <f t="shared" si="173"/>
+        <f>SUM(J201:J206)</f>
         <v>10198.51</v>
       </c>
       <c r="K207" s="119">
@@ -28382,8 +28407,9 @@
         <v>10198.51</v>
       </c>
       <c r="Y207" s="245"/>
-    </row>
-    <row r="208" spans="1:25" s="124" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z207" s="342"/>
+    </row>
+    <row r="208" spans="1:26" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="60">
         <f>A201+1</f>
         <v>46052</v>
@@ -28454,7 +28480,7 @@
       </c>
     </row>
     <row r="209" spans="1:28" s="124" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="367" t="s">
+      <c r="A209" s="350" t="s">
         <v>180</v>
       </c>
       <c r="B209" s="299">
@@ -28521,7 +28547,7 @@
       </c>
     </row>
     <row r="210" spans="1:28" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="367"/>
+      <c r="A210" s="350"/>
       <c r="B210" s="299">
         <v>33</v>
       </c>
@@ -28588,7 +28614,7 @@
       </c>
     </row>
     <row r="211" spans="1:28" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="367"/>
+      <c r="A211" s="350"/>
       <c r="B211" s="299">
         <v>32</v>
       </c>
@@ -28655,7 +28681,7 @@
       </c>
     </row>
     <row r="212" spans="1:28" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="367"/>
+      <c r="A212" s="350"/>
       <c r="B212" s="299">
         <v>0</v>
       </c>
@@ -28720,7 +28746,7 @@
       </c>
     </row>
     <row r="213" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="367"/>
+      <c r="A213" s="350"/>
       <c r="B213" s="299">
         <v>1</v>
       </c>
@@ -28816,7 +28842,7 @@
         <v>185</v>
       </c>
       <c r="J214" s="120">
-        <f t="shared" si="179"/>
+        <f>SUM(J208:J213)</f>
         <v>9022.23</v>
       </c>
       <c r="K214" s="119">
@@ -28855,6 +28881,7 @@
         <v>10198.51</v>
       </c>
       <c r="Y214" s="259"/>
+      <c r="Z214" s="342"/>
     </row>
     <row r="215" spans="1:28" s="124" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="60">
@@ -29291,7 +29318,7 @@
         <v>147</v>
       </c>
       <c r="J221" s="120">
-        <f t="shared" si="184"/>
+        <f>SUM(J215:J220)</f>
         <v>6469.5</v>
       </c>
       <c r="K221" s="119">
@@ -29330,45 +29357,47 @@
         <v>6469.5</v>
       </c>
       <c r="Y221" s="290"/>
+      <c r="Z221" s="342"/>
       <c r="AB221" s="172"/>
     </row>
     <row r="222" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="223" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223"/>
-      <c r="B223" s="361" t="s">
+      <c r="B223" s="353" t="s">
         <v>56</v>
       </c>
-      <c r="C223" s="362"/>
-      <c r="D223" s="362"/>
-      <c r="E223" s="362"/>
-      <c r="F223" s="362"/>
-      <c r="G223" s="363"/>
+      <c r="C223" s="354"/>
+      <c r="D223" s="354"/>
+      <c r="E223" s="354"/>
+      <c r="F223" s="354"/>
+      <c r="G223" s="355"/>
       <c r="H223" s="293"/>
-      <c r="I223" s="361" t="s">
+      <c r="I223" s="353" t="s">
         <v>57</v>
       </c>
-      <c r="J223" s="362"/>
-      <c r="K223" s="362"/>
-      <c r="L223" s="362"/>
-      <c r="M223" s="362"/>
-      <c r="N223" s="363"/>
-      <c r="P223" s="359" t="s">
+      <c r="J223" s="354"/>
+      <c r="K223" s="354"/>
+      <c r="L223" s="354"/>
+      <c r="M223" s="354"/>
+      <c r="N223" s="355"/>
+      <c r="P223" s="361" t="s">
         <v>139</v>
       </c>
-      <c r="Q223" s="359"/>
-      <c r="R223" s="359"/>
-      <c r="S223" s="360"/>
-      <c r="T223" s="355" t="s">
+      <c r="Q223" s="361"/>
+      <c r="R223" s="361"/>
+      <c r="S223" s="362"/>
+      <c r="T223" s="374" t="s">
         <v>142</v>
       </c>
-      <c r="U223" s="356"/>
-      <c r="V223" s="357"/>
-      <c r="W223" s="346" t="s">
+      <c r="U223" s="375"/>
+      <c r="V223" s="376"/>
+      <c r="W223" s="366" t="s">
         <v>143</v>
       </c>
-      <c r="X223" s="346" t="s">
+      <c r="X223" s="366" t="s">
         <v>162</v>
       </c>
+      <c r="Z223" s="342"/>
       <c r="AB223" s="124">
         <v>279938.09000000003</v>
       </c>
@@ -29435,8 +29464,8 @@
       <c r="V224" s="229" t="s">
         <v>146</v>
       </c>
-      <c r="W224" s="347"/>
-      <c r="X224" s="347"/>
+      <c r="W224" s="367"/>
+      <c r="X224" s="367"/>
     </row>
     <row r="225" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
@@ -29522,7 +29551,7 @@
       </c>
       <c r="W225" s="233">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214+W221</f>
-        <v>280125.7</v>
+        <v>280430.81</v>
       </c>
       <c r="X225" s="233">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214+X221</f>
@@ -29946,10 +29975,10 @@
     </row>
     <row r="235" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A235" s="24"/>
-      <c r="B235" s="368" t="s">
+      <c r="B235" s="351" t="s">
         <v>55</v>
       </c>
-      <c r="C235" s="369"/>
+      <c r="C235" s="352"/>
       <c r="D235" s="25" t="s">
         <v>65</v>
       </c>
@@ -30130,16 +30159,15 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="32">
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="B235:C235"/>
-    <mergeCell ref="B223:G223"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="A90:A94"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="A160:A164"/>
-    <mergeCell ref="A209:A213"/>
+    <mergeCell ref="X223:X224"/>
+    <mergeCell ref="W223:W224"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="T223:V223"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="X3:X4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="P223:S223"/>
     <mergeCell ref="N3:N4"/>
@@ -30153,15 +30181,16 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="X223:X224"/>
-    <mergeCell ref="W223:W224"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="T223:V223"/>
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="B235:C235"/>
+    <mergeCell ref="B223:G223"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A90:A94"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="A160:A164"/>
+    <mergeCell ref="A209:A213"/>
   </mergeCells>
   <conditionalFormatting sqref="D33:E38">
     <cfRule type="expression" dxfId="46" priority="115">
@@ -34353,130 +34382,130 @@
   <sheetData>
     <row r="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="C1" s="8"/>
-      <c r="D1" s="373">
+      <c r="D1" s="377">
         <v>46023</v>
       </c>
-      <c r="E1" s="373"/>
-      <c r="F1" s="373">
+      <c r="E1" s="377"/>
+      <c r="F1" s="377">
         <v>46024</v>
       </c>
-      <c r="G1" s="373"/>
-      <c r="H1" s="373">
+      <c r="G1" s="377"/>
+      <c r="H1" s="377">
         <v>46025</v>
       </c>
-      <c r="I1" s="373"/>
-      <c r="J1" s="373">
+      <c r="I1" s="377"/>
+      <c r="J1" s="377">
         <v>46026</v>
       </c>
-      <c r="K1" s="373"/>
-      <c r="L1" s="373">
+      <c r="K1" s="377"/>
+      <c r="L1" s="377">
         <v>46027</v>
       </c>
-      <c r="M1" s="373"/>
-      <c r="N1" s="373">
+      <c r="M1" s="377"/>
+      <c r="N1" s="377">
         <v>46028</v>
       </c>
-      <c r="O1" s="373"/>
-      <c r="P1" s="373">
+      <c r="O1" s="377"/>
+      <c r="P1" s="377">
         <v>46029</v>
       </c>
-      <c r="Q1" s="373"/>
-      <c r="R1" s="373">
+      <c r="Q1" s="377"/>
+      <c r="R1" s="377">
         <v>46030</v>
       </c>
-      <c r="S1" s="373"/>
-      <c r="T1" s="373">
+      <c r="S1" s="377"/>
+      <c r="T1" s="377">
         <v>46031</v>
       </c>
-      <c r="U1" s="373"/>
-      <c r="V1" s="373">
+      <c r="U1" s="377"/>
+      <c r="V1" s="377">
         <v>46032</v>
       </c>
-      <c r="W1" s="373"/>
-      <c r="X1" s="373">
+      <c r="W1" s="377"/>
+      <c r="X1" s="377">
         <v>46033</v>
       </c>
-      <c r="Y1" s="373"/>
-      <c r="Z1" s="373">
+      <c r="Y1" s="377"/>
+      <c r="Z1" s="377">
         <v>46034</v>
       </c>
-      <c r="AA1" s="373"/>
-      <c r="AB1" s="373">
+      <c r="AA1" s="377"/>
+      <c r="AB1" s="377">
         <v>46035</v>
       </c>
-      <c r="AC1" s="373"/>
-      <c r="AD1" s="373">
+      <c r="AC1" s="377"/>
+      <c r="AD1" s="377">
         <v>46036</v>
       </c>
-      <c r="AE1" s="373"/>
-      <c r="AF1" s="373">
+      <c r="AE1" s="377"/>
+      <c r="AF1" s="377">
         <v>46037</v>
       </c>
-      <c r="AG1" s="373"/>
-      <c r="AH1" s="373">
+      <c r="AG1" s="377"/>
+      <c r="AH1" s="377">
         <v>46038</v>
       </c>
-      <c r="AI1" s="373"/>
-      <c r="AJ1" s="373">
+      <c r="AI1" s="377"/>
+      <c r="AJ1" s="377">
         <v>46039</v>
       </c>
-      <c r="AK1" s="373"/>
-      <c r="AL1" s="373">
+      <c r="AK1" s="377"/>
+      <c r="AL1" s="377">
         <v>46040</v>
       </c>
-      <c r="AM1" s="373"/>
-      <c r="AN1" s="373">
+      <c r="AM1" s="377"/>
+      <c r="AN1" s="377">
         <v>46041</v>
       </c>
-      <c r="AO1" s="373"/>
-      <c r="AP1" s="373">
+      <c r="AO1" s="377"/>
+      <c r="AP1" s="377">
         <v>46042</v>
       </c>
-      <c r="AQ1" s="373"/>
-      <c r="AR1" s="373">
+      <c r="AQ1" s="377"/>
+      <c r="AR1" s="377">
         <v>46043</v>
       </c>
-      <c r="AS1" s="373"/>
-      <c r="AT1" s="373">
+      <c r="AS1" s="377"/>
+      <c r="AT1" s="377">
         <v>46044</v>
       </c>
-      <c r="AU1" s="373"/>
-      <c r="AV1" s="373">
+      <c r="AU1" s="377"/>
+      <c r="AV1" s="377">
         <v>46045</v>
       </c>
-      <c r="AW1" s="373"/>
-      <c r="AX1" s="373">
+      <c r="AW1" s="377"/>
+      <c r="AX1" s="377">
         <v>46046</v>
       </c>
-      <c r="AY1" s="373"/>
-      <c r="AZ1" s="373">
+      <c r="AY1" s="377"/>
+      <c r="AZ1" s="377">
         <v>46047</v>
       </c>
-      <c r="BA1" s="373"/>
-      <c r="BB1" s="373">
+      <c r="BA1" s="377"/>
+      <c r="BB1" s="377">
         <v>46048</v>
       </c>
-      <c r="BC1" s="373"/>
-      <c r="BD1" s="373">
+      <c r="BC1" s="377"/>
+      <c r="BD1" s="377">
         <v>46049</v>
       </c>
-      <c r="BE1" s="373"/>
-      <c r="BF1" s="373">
+      <c r="BE1" s="377"/>
+      <c r="BF1" s="377">
         <v>46050</v>
       </c>
-      <c r="BG1" s="373"/>
-      <c r="BH1" s="373">
+      <c r="BG1" s="377"/>
+      <c r="BH1" s="377">
         <v>46051</v>
       </c>
-      <c r="BI1" s="373"/>
-      <c r="BJ1" s="373">
+      <c r="BI1" s="377"/>
+      <c r="BJ1" s="377">
         <v>46052</v>
       </c>
-      <c r="BK1" s="373"/>
-      <c r="BL1" s="373">
+      <c r="BK1" s="377"/>
+      <c r="BL1" s="377">
         <v>46053</v>
       </c>
-      <c r="BM1" s="373"/>
+      <c r="BM1" s="377"/>
     </row>
     <row r="2" spans="1:65" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="8"/>
@@ -40414,10 +40443,10 @@
       </c>
     </row>
     <row r="37" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A37" s="374" t="s">
+      <c r="A37" s="378" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="374"/>
+      <c r="B37" s="378"/>
       <c r="C37" s="8"/>
       <c r="D37" s="149">
         <f>SUM(D31:D36)</f>
@@ -43092,6 +43121,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="BJ1:BK1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AZ1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="BL1:BM1"/>
     <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="AV1:AW1"/>
@@ -43108,22 +43153,6 @@
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="BJ1:BK1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -43149,19 +43178,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="375" t="s">
+      <c r="A2" s="379" t="s">
         <v>177</v>
       </c>
-      <c r="B2" s="376"/>
-      <c r="C2" s="376"/>
-      <c r="D2" s="376"/>
-      <c r="E2" s="376"/>
-      <c r="F2" s="376"/>
-      <c r="G2" s="376"/>
-      <c r="H2" s="376"/>
-      <c r="I2" s="376"/>
-      <c r="J2" s="376"/>
-      <c r="K2" s="376"/>
+      <c r="B2" s="380"/>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
+      <c r="F2" s="380"/>
+      <c r="G2" s="380"/>
+      <c r="H2" s="380"/>
+      <c r="I2" s="380"/>
+      <c r="J2" s="380"/>
+      <c r="K2" s="380"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="158" t="s">
@@ -43202,7 +43231,7 @@
       <c r="A4" s="160">
         <v>46023</v>
       </c>
-      <c r="B4" s="387">
+      <c r="B4" s="345">
         <f>'KM-Servicio'!N11</f>
         <v>5372</v>
       </c>
@@ -43210,7 +43239,7 @@
         <f>B4</f>
         <v>5372</v>
       </c>
-      <c r="D4" s="389">
+      <c r="D4" s="347">
         <f>'KM-Servicio'!W11</f>
         <v>5003.08</v>
       </c>
@@ -43244,7 +43273,7 @@
       <c r="A5" s="160">
         <v>46024</v>
       </c>
-      <c r="B5" s="387">
+      <c r="B5" s="345">
         <f>'KM-Servicio'!N18</f>
         <v>11904</v>
       </c>
@@ -43252,7 +43281,7 @@
         <f>B5+C4</f>
         <v>17276</v>
       </c>
-      <c r="D5" s="389">
+      <c r="D5" s="347">
         <f>'KM-Servicio'!W18</f>
         <v>11439.220000000001</v>
       </c>
@@ -43286,7 +43315,7 @@
       <c r="A6" s="160">
         <v>46025</v>
       </c>
-      <c r="B6" s="387">
+      <c r="B6" s="345">
         <f>'KM-Servicio'!N25</f>
         <v>6613</v>
       </c>
@@ -43294,7 +43323,7 @@
         <f t="shared" ref="C6:C31" si="0">B6+C5</f>
         <v>23889</v>
       </c>
-      <c r="D6" s="389">
+      <c r="D6" s="347">
         <f>'KM-Servicio'!W25</f>
         <v>6469.5</v>
       </c>
@@ -43328,7 +43357,7 @@
       <c r="A7" s="160">
         <v>46026</v>
       </c>
-      <c r="B7" s="387">
+      <c r="B7" s="345">
         <f>'KM-Servicio'!N32</f>
         <v>5001</v>
       </c>
@@ -43336,7 +43365,7 @@
         <f t="shared" si="0"/>
         <v>28890</v>
       </c>
-      <c r="D7" s="389">
+      <c r="D7" s="347">
         <f>'KM-Servicio'!W32</f>
         <v>4916.8200000000006</v>
       </c>
@@ -43370,7 +43399,7 @@
       <c r="A8" s="160">
         <v>46027</v>
       </c>
-      <c r="B8" s="387">
+      <c r="B8" s="345">
         <f>'KM-Servicio'!N39</f>
         <v>11922</v>
       </c>
@@ -43378,7 +43407,7 @@
         <f t="shared" si="0"/>
         <v>40812</v>
       </c>
-      <c r="D8" s="389">
+      <c r="D8" s="347">
         <f>'KM-Servicio'!W39</f>
         <v>11439.220000000001</v>
       </c>
@@ -43412,7 +43441,7 @@
       <c r="A9" s="160">
         <v>46028</v>
       </c>
-      <c r="B9" s="388">
+      <c r="B9" s="346">
         <f>'KM-Servicio'!N46</f>
         <v>11975</v>
       </c>
@@ -43420,7 +43449,7 @@
         <f t="shared" si="0"/>
         <v>52787</v>
       </c>
-      <c r="D9" s="390">
+      <c r="D9" s="348">
         <f>'KM-Servicio'!W46</f>
         <v>11350.57</v>
       </c>
@@ -43454,7 +43483,7 @@
       <c r="A10" s="160">
         <v>46029</v>
       </c>
-      <c r="B10" s="388">
+      <c r="B10" s="346">
         <f>'KM-Servicio'!N53</f>
         <v>11899</v>
       </c>
@@ -43462,17 +43491,17 @@
         <f t="shared" si="0"/>
         <v>64686</v>
       </c>
-      <c r="D10" s="390">
+      <c r="D10" s="348">
         <f>'KM-Servicio'!W53</f>
-        <v>11064.06</v>
+        <v>11342.65</v>
       </c>
       <c r="E10" s="334">
         <f t="shared" si="1"/>
-        <v>61682.47</v>
+        <v>61961.060000000005</v>
       </c>
       <c r="F10" s="335">
         <f>'KM-Servicio'!O53</f>
-        <v>92.983107824186902</v>
+        <v>95.324397008151934</v>
       </c>
       <c r="G10" s="336">
         <f>SUM('KM-Servicio'!B53:C53)</f>
@@ -43496,7 +43525,7 @@
       <c r="A11" s="160">
         <v>46030</v>
       </c>
-      <c r="B11" s="388">
+      <c r="B11" s="346">
         <f>'KM-Servicio'!N60</f>
         <v>12321</v>
       </c>
@@ -43504,13 +43533,13 @@
         <f t="shared" si="0"/>
         <v>77007</v>
       </c>
-      <c r="D11" s="390">
+      <c r="D11" s="348">
         <f>'KM-Servicio'!W60</f>
         <v>11592.439999999999</v>
       </c>
       <c r="E11" s="334">
         <f t="shared" si="1"/>
-        <v>73274.91</v>
+        <v>73553.5</v>
       </c>
       <c r="F11" s="335">
         <f>'KM-Servicio'!O60</f>
@@ -43538,7 +43567,7 @@
       <c r="A12" s="160">
         <v>46031</v>
       </c>
-      <c r="B12" s="387">
+      <c r="B12" s="345">
         <f>'KM-Servicio'!N67</f>
         <v>12431</v>
       </c>
@@ -43546,13 +43575,13 @@
         <f t="shared" si="0"/>
         <v>89438</v>
       </c>
-      <c r="D12" s="389">
+      <c r="D12" s="347">
         <f>'KM-Servicio'!W67</f>
         <v>11574.710000000001</v>
       </c>
       <c r="E12" s="12">
         <f t="shared" si="1"/>
-        <v>84849.62000000001</v>
+        <v>85128.21</v>
       </c>
       <c r="F12" s="166">
         <f>'KM-Servicio'!O67</f>
@@ -43580,7 +43609,7 @@
       <c r="A13" s="160">
         <v>46032</v>
       </c>
-      <c r="B13" s="387">
+      <c r="B13" s="345">
         <f>'KM-Servicio'!N74</f>
         <v>6491</v>
       </c>
@@ -43588,13 +43617,13 @@
         <f t="shared" si="0"/>
         <v>95929</v>
       </c>
-      <c r="D13" s="389">
+      <c r="D13" s="347">
         <f>'KM-Servicio'!W74</f>
         <v>6469.5</v>
       </c>
       <c r="E13" s="12">
         <f t="shared" si="1"/>
-        <v>91319.12000000001</v>
+        <v>91597.71</v>
       </c>
       <c r="F13" s="166">
         <f>'KM-Servicio'!O74</f>
@@ -43622,7 +43651,7 @@
       <c r="A14" s="160">
         <v>46033</v>
       </c>
-      <c r="B14" s="387">
+      <c r="B14" s="345">
         <f>'KM-Servicio'!N81</f>
         <v>4999</v>
       </c>
@@ -43630,13 +43659,13 @@
         <f t="shared" si="0"/>
         <v>100928</v>
       </c>
-      <c r="D14" s="389">
+      <c r="D14" s="347">
         <f>'KM-Servicio'!W81</f>
         <v>4916.8200000000006</v>
       </c>
       <c r="E14" s="12">
         <f t="shared" si="1"/>
-        <v>96235.940000000017</v>
+        <v>96514.530000000013</v>
       </c>
       <c r="F14" s="166">
         <f>'KM-Servicio'!O81</f>
@@ -43664,7 +43693,7 @@
       <c r="A15" s="160">
         <v>46034</v>
       </c>
-      <c r="B15" s="387">
+      <c r="B15" s="345">
         <f>'KM-Servicio'!N88</f>
         <v>12215</v>
       </c>
@@ -43672,13 +43701,13 @@
         <f t="shared" si="0"/>
         <v>113143</v>
       </c>
-      <c r="D15" s="389">
+      <c r="D15" s="347">
         <f>'KM-Servicio'!W88</f>
         <v>11421.49</v>
       </c>
       <c r="E15" s="12">
         <f t="shared" si="1"/>
-        <v>107657.43000000002</v>
+        <v>107936.02000000002</v>
       </c>
       <c r="F15" s="166">
         <f>'KM-Servicio'!O88</f>
@@ -43706,7 +43735,7 @@
       <c r="A16" s="160">
         <v>46035</v>
       </c>
-      <c r="B16" s="388">
+      <c r="B16" s="346">
         <f>'KM-Servicio'!N95</f>
         <v>10392</v>
       </c>
@@ -43714,17 +43743,17 @@
         <f t="shared" si="0"/>
         <v>123535</v>
       </c>
-      <c r="D16" s="390">
+      <c r="D16" s="348">
         <f>'KM-Servicio'!W95</f>
-        <v>9823.4200000000019</v>
+        <v>9849.94</v>
       </c>
       <c r="E16" s="334">
         <f t="shared" si="1"/>
-        <v>117480.85000000002</v>
+        <v>117785.96000000002</v>
       </c>
       <c r="F16" s="335">
         <f>'KM-Servicio'!O95</f>
-        <v>94.52867590454197</v>
+        <v>94.783872209391845</v>
       </c>
       <c r="G16" s="336">
         <f>SUM('KM-Servicio'!B95:C95)</f>
@@ -43748,7 +43777,7 @@
       <c r="A17" s="160">
         <v>46036</v>
       </c>
-      <c r="B17" s="388">
+      <c r="B17" s="346">
         <f>'KM-Servicio'!N102</f>
         <v>11104</v>
       </c>
@@ -43756,13 +43785,13 @@
         <f t="shared" si="0"/>
         <v>134639</v>
       </c>
-      <c r="D17" s="390">
+      <c r="D17" s="348">
         <f>'KM-Servicio'!W102</f>
         <v>10556.5</v>
       </c>
       <c r="E17" s="334">
         <f t="shared" si="1"/>
-        <v>128037.35000000002</v>
+        <v>128342.46000000002</v>
       </c>
       <c r="F17" s="335">
         <f>'KM-Servicio'!O102</f>
@@ -43790,7 +43819,7 @@
       <c r="A18" s="160">
         <v>46037</v>
       </c>
-      <c r="B18" s="387">
+      <c r="B18" s="345">
         <f>'KM-Servicio'!N109</f>
         <v>11137</v>
       </c>
@@ -43798,13 +43827,13 @@
         <f t="shared" si="0"/>
         <v>145776</v>
       </c>
-      <c r="D18" s="389">
+      <c r="D18" s="347">
         <f>'KM-Servicio'!W109</f>
         <v>10591.96</v>
       </c>
       <c r="E18" s="12">
         <f t="shared" si="1"/>
-        <v>138629.31000000003</v>
+        <v>138934.42000000001</v>
       </c>
       <c r="F18" s="166">
         <f>'KM-Servicio'!O109</f>
@@ -43832,7 +43861,7 @@
       <c r="A19" s="160">
         <v>46038</v>
       </c>
-      <c r="B19" s="387">
+      <c r="B19" s="345">
         <f>'KM-Servicio'!$N$116</f>
         <v>11217</v>
       </c>
@@ -43840,13 +43869,13 @@
         <f t="shared" si="0"/>
         <v>156993</v>
       </c>
-      <c r="D19" s="389">
+      <c r="D19" s="347">
         <f>'KM-Servicio'!$W$116</f>
         <v>10523.43</v>
       </c>
       <c r="E19" s="12">
         <f t="shared" si="1"/>
-        <v>149152.74000000002</v>
+        <v>149457.85</v>
       </c>
       <c r="F19" s="166">
         <f>'KM-Servicio'!O116</f>
@@ -43873,7 +43902,7 @@
       <c r="A20" s="160">
         <v>46039</v>
       </c>
-      <c r="B20" s="387">
+      <c r="B20" s="345">
         <f>'KM-Servicio'!$N$123</f>
         <v>6798</v>
       </c>
@@ -43881,13 +43910,13 @@
         <f t="shared" si="0"/>
         <v>163791</v>
       </c>
-      <c r="D20" s="389">
+      <c r="D20" s="347">
         <f>'KM-Servicio'!$W$123</f>
         <v>6469.5</v>
       </c>
       <c r="E20" s="12">
         <f t="shared" si="1"/>
-        <v>155622.24000000002</v>
+        <v>155927.35</v>
       </c>
       <c r="F20" s="166">
         <f>'KM-Servicio'!O123</f>
@@ -43915,7 +43944,7 @@
       <c r="A21" s="160">
         <v>46040</v>
       </c>
-      <c r="B21" s="387">
+      <c r="B21" s="345">
         <f>'KM-Servicio'!N130</f>
         <v>4868</v>
       </c>
@@ -43923,13 +43952,13 @@
         <f t="shared" si="0"/>
         <v>168659</v>
       </c>
-      <c r="D21" s="389">
+      <c r="D21" s="347">
         <f>'KM-Servicio'!$W$130</f>
         <v>4830.5600000000004</v>
       </c>
       <c r="E21" s="12">
         <f t="shared" si="1"/>
-        <v>160452.80000000002</v>
+        <v>160757.91</v>
       </c>
       <c r="F21" s="166">
         <f>'KM-Servicio'!O130</f>
@@ -43957,7 +43986,7 @@
       <c r="A22" s="160">
         <v>46041</v>
       </c>
-      <c r="B22" s="387">
+      <c r="B22" s="345">
         <f>'KM-Servicio'!N137</f>
         <v>11010</v>
       </c>
@@ -43965,13 +43994,13 @@
         <f t="shared" si="0"/>
         <v>179669</v>
       </c>
-      <c r="D22" s="389">
+      <c r="D22" s="347">
         <f>'KM-Servicio'!$W$137</f>
         <v>10574.23</v>
       </c>
       <c r="E22" s="12">
         <f t="shared" si="1"/>
-        <v>171027.03000000003</v>
+        <v>171332.14</v>
       </c>
       <c r="F22" s="171">
         <f>'KM-Servicio'!O137</f>
@@ -43999,7 +44028,7 @@
       <c r="A23" s="160">
         <v>46042</v>
       </c>
-      <c r="B23" s="388">
+      <c r="B23" s="346">
         <f>'KM-Servicio'!N144</f>
         <v>11092</v>
       </c>
@@ -44007,13 +44036,13 @@
         <f t="shared" si="0"/>
         <v>190761</v>
       </c>
-      <c r="D23" s="390">
+      <c r="D23" s="348">
         <f>'KM-Servicio'!$W$144</f>
         <v>10609.69</v>
       </c>
       <c r="E23" s="334">
         <f t="shared" si="1"/>
-        <v>181636.72000000003</v>
+        <v>181941.83000000002</v>
       </c>
       <c r="F23" s="335">
         <f>'KM-Servicio'!O144</f>
@@ -44041,7 +44070,7 @@
       <c r="A24" s="160">
         <v>46043</v>
       </c>
-      <c r="B24" s="388">
+      <c r="B24" s="346">
         <f>'KM-Servicio'!N151</f>
         <v>10958</v>
       </c>
@@ -44049,13 +44078,13 @@
         <f t="shared" si="0"/>
         <v>201719</v>
       </c>
-      <c r="D24" s="390">
+      <c r="D24" s="348">
         <f>'KM-Servicio'!$W$151</f>
         <v>10574.23</v>
       </c>
       <c r="E24" s="334">
         <f t="shared" si="1"/>
-        <v>192210.95000000004</v>
+        <v>192516.06000000003</v>
       </c>
       <c r="F24" s="335">
         <f>'KM-Servicio'!O151</f>
@@ -44083,7 +44112,7 @@
       <c r="A25" s="160">
         <v>46044</v>
       </c>
-      <c r="B25" s="387">
+      <c r="B25" s="345">
         <f>'KM-Servicio'!N158</f>
         <v>10861</v>
       </c>
@@ -44091,13 +44120,13 @@
         <f t="shared" si="0"/>
         <v>212580</v>
       </c>
-      <c r="D25" s="389">
+      <c r="D25" s="347">
         <f>'KM-Servicio'!$W$158</f>
         <v>10485.58</v>
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>202696.53000000003</v>
+        <v>203001.64</v>
       </c>
       <c r="F25" s="166">
         <f>'KM-Servicio'!O158</f>
@@ -44125,7 +44154,7 @@
       <c r="A26" s="160">
         <v>46045</v>
       </c>
-      <c r="B26" s="387">
+      <c r="B26" s="345">
         <f>'KM-Servicio'!N165</f>
         <v>10805</v>
       </c>
@@ -44133,13 +44162,13 @@
         <f t="shared" si="0"/>
         <v>223385</v>
       </c>
-      <c r="D26" s="389">
+      <c r="D26" s="347">
         <f>'KM-Servicio'!$W$165</f>
         <v>10339.779999999999</v>
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>213036.31000000003</v>
+        <v>213341.42</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O165</f>
@@ -44167,7 +44196,7 @@
       <c r="A27" s="160">
         <v>46046</v>
       </c>
-      <c r="B27" s="387">
+      <c r="B27" s="345">
         <f>'KM-Servicio'!N172</f>
         <v>6602</v>
       </c>
@@ -44175,13 +44204,13 @@
         <f t="shared" si="0"/>
         <v>229987</v>
       </c>
-      <c r="D27" s="389">
+      <c r="D27" s="347">
         <f>'KM-Servicio'!$W$172</f>
         <v>6469.5</v>
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>219505.81000000003</v>
+        <v>219810.92</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O172</f>
@@ -44209,7 +44238,7 @@
       <c r="A28" s="160">
         <v>46047</v>
       </c>
-      <c r="B28" s="388">
+      <c r="B28" s="346">
         <f>'KM-Servicio'!N179</f>
         <v>5033</v>
       </c>
@@ -44217,13 +44246,13 @@
         <f t="shared" si="0"/>
         <v>235020</v>
       </c>
-      <c r="D28" s="390">
+      <c r="D28" s="348">
         <f>'KM-Servicio'!$W$179</f>
         <v>4916.8200000000006</v>
       </c>
       <c r="E28" s="334">
         <f t="shared" si="1"/>
-        <v>224422.63000000003</v>
+        <v>224727.74000000002</v>
       </c>
       <c r="F28" s="335">
         <f>'KM-Servicio'!O179</f>
@@ -44251,7 +44280,7 @@
       <c r="A29" s="160">
         <v>46048</v>
       </c>
-      <c r="B29" s="387">
+      <c r="B29" s="345">
         <f>'KM-Servicio'!N186</f>
         <v>10457</v>
       </c>
@@ -44259,13 +44288,13 @@
         <f t="shared" si="0"/>
         <v>245477</v>
       </c>
-      <c r="D29" s="389">
+      <c r="D29" s="347">
         <f>'KM-Servicio'!$W$186</f>
         <v>10023.6</v>
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>234446.23000000004</v>
+        <v>234751.34000000003</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O186</f>
@@ -44293,7 +44322,7 @@
       <c r="A30" s="160">
         <v>46049</v>
       </c>
-      <c r="B30" s="388">
+      <c r="B30" s="346">
         <f>'KM-Servicio'!N193</f>
         <v>10510</v>
       </c>
@@ -44301,13 +44330,13 @@
         <f t="shared" si="0"/>
         <v>255987</v>
       </c>
-      <c r="D30" s="390">
+      <c r="D30" s="348">
         <f>'KM-Servicio'!$W$193</f>
         <v>10074.4</v>
       </c>
       <c r="E30" s="334">
         <f t="shared" si="1"/>
-        <v>244520.63000000003</v>
+        <v>244825.74000000002</v>
       </c>
       <c r="F30" s="335">
         <f>'KM-Servicio'!O193</f>
@@ -44335,7 +44364,7 @@
       <c r="A31" s="160">
         <v>46050</v>
       </c>
-      <c r="B31" s="388">
+      <c r="B31" s="346">
         <f>'KM-Servicio'!N200</f>
         <v>10451</v>
       </c>
@@ -44343,13 +44372,13 @@
         <f t="shared" si="0"/>
         <v>266438</v>
       </c>
-      <c r="D31" s="390">
+      <c r="D31" s="348">
         <f>'KM-Servicio'!$W$200</f>
         <v>10109.86</v>
       </c>
       <c r="E31" s="334">
         <f t="shared" si="1"/>
-        <v>254630.49000000005</v>
+        <v>254935.60000000003</v>
       </c>
       <c r="F31" s="335">
         <f>'KM-Servicio'!O200</f>
@@ -44377,7 +44406,7 @@
       <c r="A32" s="160">
         <v>46051</v>
       </c>
-      <c r="B32" s="387">
+      <c r="B32" s="345">
         <f>'KM-Servicio'!N207</f>
         <v>10502</v>
       </c>
@@ -44385,13 +44414,13 @@
         <f>B32+C31</f>
         <v>276940</v>
       </c>
-      <c r="D32" s="389">
+      <c r="D32" s="347">
         <f>'KM-Servicio'!$W$207</f>
         <v>10056.67</v>
       </c>
       <c r="E32" s="12">
         <f>D32+E31</f>
-        <v>264687.16000000003</v>
+        <v>264992.27</v>
       </c>
       <c r="F32" s="166">
         <f>'KM-Servicio'!O207</f>
@@ -44419,7 +44448,7 @@
       <c r="A33" s="160">
         <v>46052</v>
       </c>
-      <c r="B33" s="387">
+      <c r="B33" s="345">
         <f>'KM-Servicio'!N214</f>
         <v>9512</v>
       </c>
@@ -44427,13 +44456,13 @@
         <f>B33+C32</f>
         <v>286452</v>
       </c>
-      <c r="D33" s="389">
+      <c r="D33" s="347">
         <f>'KM-Servicio'!$W$214</f>
         <v>8969.0400000000009</v>
       </c>
       <c r="E33" s="12">
         <f>D33+E32</f>
-        <v>273656.2</v>
+        <v>273961.31</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O214</f>
@@ -44463,7 +44492,7 @@
       <c r="A34" s="160">
         <v>46053</v>
       </c>
-      <c r="B34" s="387">
+      <c r="B34" s="345">
         <f>'KM-Servicio'!N221</f>
         <v>6500</v>
       </c>
@@ -44471,13 +44500,13 @@
         <f>B34+C33</f>
         <v>292952</v>
       </c>
-      <c r="D34" s="389">
+      <c r="D34" s="347">
         <f>'KM-Servicio'!$W$221</f>
         <v>6469.5</v>
       </c>
       <c r="E34" s="12">
         <f>D34+E33</f>
-        <v>280125.7</v>
+        <v>280430.81</v>
       </c>
       <c r="F34" s="166">
         <f>'KM-Servicio'!O221</f>
@@ -44533,15 +44562,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>280125.7</v>
+        <v>280430.81</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>4483069.2200000007</v>
+        <v>4490537.8499999996</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>95.963984929599235</v>
+        <v>96.047742526012627</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -44585,12 +44614,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="377" t="s">
+      <c r="A3" s="382" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="378"/>
-      <c r="C3" s="378"/>
-      <c r="D3" s="379"/>
+      <c r="B3" s="383"/>
+      <c r="C3" s="383"/>
+      <c r="D3" s="384"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -44736,12 +44765,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="380" t="s">
+      <c r="A13" s="385" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="381"/>
-      <c r="C13" s="381"/>
-      <c r="D13" s="382"/>
+      <c r="B13" s="386"/>
+      <c r="C13" s="386"/>
+      <c r="D13" s="387"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -44788,8 +44817,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="386"/>
-      <c r="H16" s="386"/>
+      <c r="G16" s="381"/>
+      <c r="H16" s="381"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -44804,8 +44833,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="386"/>
-      <c r="H17" s="386"/>
+      <c r="G17" s="381"/>
+      <c r="H17" s="381"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -44820,8 +44849,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="386"/>
-      <c r="H18" s="386"/>
+      <c r="G18" s="381"/>
+      <c r="H18" s="381"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -44835,8 +44864,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="386"/>
-      <c r="H19" s="386"/>
+      <c r="G19" s="381"/>
+      <c r="H19" s="381"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -44850,8 +44879,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="386"/>
-      <c r="H20" s="386"/>
+      <c r="G20" s="381"/>
+      <c r="H20" s="381"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -44865,8 +44894,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="386"/>
-      <c r="H21" s="386"/>
+      <c r="G21" s="381"/>
+      <c r="H21" s="381"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -44891,9 +44920,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="383"/>
-      <c r="C23" s="384"/>
-      <c r="D23" s="385"/>
+      <c r="B23" s="388"/>
+      <c r="C23" s="389"/>
+      <c r="D23" s="390"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -44905,10 +44934,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="380"/>
-      <c r="B24" s="381"/>
-      <c r="C24" s="381"/>
-      <c r="D24" s="382"/>
+      <c r="A24" s="385"/>
+      <c r="B24" s="386"/>
+      <c r="C24" s="386"/>
+      <c r="D24" s="387"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -45021,9 +45050,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="383"/>
-      <c r="C34" s="384"/>
-      <c r="D34" s="385"/>
+      <c r="B34" s="388"/>
+      <c r="C34" s="389"/>
+      <c r="D34" s="390"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -45156,17 +45185,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -45421,15 +45450,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
@@ -45449,14 +45469,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A030680-F478-49A6-8F2D-8DF406779E4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A030680-F478-49A6-8F2D-8DF406779E4C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8FC54E6-627C-4D78-AB4A-0BD56A4CBDEF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18BEA5DD-DF52-415D-9F6B-C403E9A1A413}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18BEA5DD-DF52-415D-9F6B-C403E9A1A413}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8FC54E6-627C-4D78-AB4A-0BD56A4CBDEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>